--- a/membership_application_form_templates/038_reseller_application_form--membership_application_form_templates.xlsx
+++ b/membership_application_form_templates/038_reseller_application_form--membership_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_data</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -528,10 +528,14 @@
           <t>Reseller Application Form</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your business name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Enter your email address</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter a valid email address</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,156 +601,184 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Enter your address</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter your address</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Enter your date of birth</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter your date of birth</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Enter your time zone</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter your time zone</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Select an option for your reseller account (yes/no)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select one option for your reseller account</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Select multiple options for your reseller account (yes/no)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select multiple options for your reseller account</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Enter your second time zone</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter your second time zone</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>note_2</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>note_2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Enter your second email address</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter a valid email address</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Select one option for your reseller account (yes/no)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select one option for your reseller account</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,41 +817,49 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Page 12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select multiple options for your reseller account</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>time_2</t>
+          <t>page_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>time_2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Enter your second phone number</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,156 +871,130 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>page_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Enter your second address</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter your address</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>select_one_2</t>
+          <t>page_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>select_one_2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Enter your second date of birth</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter your date of birth</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_multiple_2</t>
+          <t>page_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>select_multiple_2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Enter your second notes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter your notes</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>phone_2</t>
+          <t>page_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Page 17</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Select one option for your reseller account</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>address_2</t>
+          <t>page_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Page 18</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Select multiple options for your reseller account</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>date_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>note_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -983,10 +1009,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1011,7 +1037,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1028,7 +1054,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1045,7 +1071,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1062,7 +1088,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1079,7 +1105,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one_2_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1096,7 +1122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one_2_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1113,7 +1139,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple_2_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1130,7 +1156,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple_2_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,6 +1165,74 @@
         </is>
       </c>
       <c r="C9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>page_17_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>page_17_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>page_18_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>page_18_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
